--- a/outputs/daily/predictions_2026-07-03.xlsx
+++ b/outputs/daily/predictions_2026-07-03.xlsx
@@ -924,31 +924,31 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.094157664223621</v>
+        <v>1.099103000907772</v>
       </c>
       <c r="N2" t="n">
-        <v>1.116337100505221</v>
+        <v>1.138891763821071</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2691611034323368</v>
+        <v>0.2643835737225136</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3348543401750905</v>
+        <v>0.331100876322777</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3959845563925727</v>
+        <v>0.4045155499547096</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3398599611718844</v>
+        <v>0.3531370079904324</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9023463041475324</v>
+        <v>0.9113378253914424</v>
       </c>
       <c r="U2" t="n">
-        <v>1.157653695852468</v>
+        <v>1.198662174608558</v>
       </c>
       <c r="V2" t="n">
         <v>0.4070432208958823</v>
@@ -966,25 +966,25 @@
         <v>0.4925384992002528</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3358031139444883</v>
+        <v>0.3325669431498165</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3172511687659101</v>
+        <v>0.3149819887264375</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3469457172896016</v>
+        <v>0.352451068123746</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.3800989569905451</v>
+        <v>0.3874556896061296</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6199010430094549</v>
+        <v>0.6125443103938704</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.460740482504974</v>
+        <v>0.46668151548987</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.539259517495026</v>
+        <v>0.53331848451013</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -992,22 +992,22 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>1.09454</v>
+        <v>1.09943</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.11441</v>
+        <v>1.136665</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.20895</v>
+        <v>2.236095</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3340803471726156</v>
+        <v>0.3313602925900183</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.3191069471114729</v>
+        <v>0.3170382665606793</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.3468127057159116</v>
+        <v>0.3516014408493024</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.3468127057159116</v>
+        <v>0.3516014408493024</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4676</v>
+        <v>0.4723</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.5324</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>0.5324</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.4921</v>
+        <v>0.4875</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.5079</v>
+        <v>0.5125</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.5079</v>
+        <v>0.5125</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.4953</v>
+        <v>0.4926</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>3.715247066712168</v>
+        <v>3.782383246886434</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.3340803471726156</v>
+        <v>0.3313602925900183</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.06491924374027874</v>
+        <v>0.06697671886750473</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.2411910298792428</v>
+        <v>0.2533316193758723</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1090,16 +1090,16 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>3.715247066712168</v>
+        <v>3.782383246886434</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.3340803471726156</v>
+        <v>0.3313602925900183</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.06491924374027874</v>
+        <v>0.06697671886750473</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.2411910298792428</v>
+        <v>0.2533316193758723</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>0.1473201986138604</v>
+        <v>0.146880716213215</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>0.1230391373034503</v>
+        <v>0.1200249920052379</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>0.1090095899696056</v>
+        <v>0.1081352971954021</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>0.1065776948052906</v>
+        <v>0.1038909423351936</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>0.07475409243929559</v>
+        <v>0.07603692634516843</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>0.07326887473104614</v>
+        <v>0.0733804708933761</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>0.06832113404089588</v>
+        <v>0.06918089231161041</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="CH2" t="n">
-        <v>0.06563328827635201</v>
+        <v>0.06443147033321137</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>0.04089638158726817</v>
+        <v>0.04178620696288891</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="CL2" t="n">
-        <v>0.02781692226819418</v>
+        <v>0.0288659430535939</v>
       </c>
     </row>
     <row r="3">
@@ -1238,31 +1238,31 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.392938212942626</v>
+        <v>2.385977632977897</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6294234976064104</v>
+        <v>0.6253840775711395</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.839629738879386</v>
+        <v>0.8420965124777858</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1148649732711805</v>
+        <v>0.1137661702615862</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04550528784943338</v>
+        <v>0.04413731726062793</v>
       </c>
       <c r="S3" t="n">
-        <v>0.590442618863571</v>
+        <v>0.585207852597005</v>
       </c>
       <c r="T3" t="n">
-        <v>2.422244395149495</v>
+        <v>2.409588795213625</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6377556048505044</v>
+        <v>0.6304112047863756</v>
       </c>
       <c r="V3" t="n">
         <v>0.8197438915786095</v>
@@ -1280,25 +1280,25 @@
         <v>0.3941454890931925</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7587569584287777</v>
+        <v>0.7585941106213789</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1693837105552607</v>
+        <v>0.1697649277186334</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.07185933101596145</v>
+        <v>0.07164096165998741</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5817836237944006</v>
+        <v>0.5793334012720718</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4182163762055994</v>
+        <v>0.4206665987279282</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4317577983856345</v>
+        <v>0.4295133362971293</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.5682422016143656</v>
+        <v>0.5704866637028707</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
@@ -1306,22 +1306,22 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>2.392595</v>
+        <v>2.3858</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.630495</v>
+        <v>0.62598</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.02309</v>
+        <v>3.01178</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.8124514972114623</v>
+        <v>0.8133974946989725</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.1365252153394906</v>
+        <v>0.1361809984264961</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.05102328744904718</v>
+        <v>0.05042150687453149</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.8124514972114623</v>
+        <v>0.8133974946989725</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4237</v>
+        <v>0.4219</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.5763</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>0.5763</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         <v>1</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.8944</v>
+        <v>0.8951</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1056</v>
+        <v>0.1049</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.8944</v>
+        <v>0.8951</v>
       </c>
       <c r="BF3" t="n">
         <v>0.6</v>
@@ -1387,16 +1387,16 @@
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>8.705874136575439</v>
+        <v>8.789959244480748</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1365252153394906</v>
+        <v>0.1361809984264961</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.02166024206831006</v>
+        <v>0.0224148281649099</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1885713412144638</v>
+        <v>0.1970254260415973</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1404,16 +1404,16 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>8.705874136575439</v>
+        <v>8.789959244480748</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1365252153394906</v>
+        <v>0.1361809984264961</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.02166024206831006</v>
+        <v>0.0224148281649099</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1885713412144638</v>
+        <v>0.1970254260415973</v>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="BT3" t="n">
-        <v>0.1393978807699784</v>
+        <v>0.1401208339547183</v>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="BV3" t="n">
-        <v>0.1111901718992338</v>
+        <v>0.1114417252433893</v>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="BX3" t="n">
-        <v>0.1091744449532046</v>
+        <v>0.1101082409910488</v>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0877403016731612</v>
+        <v>0.08762933849127029</v>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="CB3" t="n">
-        <v>0.08066596230396811</v>
+        <v>0.08079897397872235</v>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="CD3" t="n">
-        <v>0.06998570689627376</v>
+        <v>0.06969388054427335</v>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="CF3" t="n">
-        <v>0.066517802810334</v>
+        <v>0.06647436595279878</v>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="CH3" t="n">
-        <v>0.05602141077572895</v>
+        <v>0.05657197623920317</v>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="CJ3" t="n">
-        <v>0.04186786809797394</v>
+        <v>0.04157201003351742</v>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="CL3" t="n">
-        <v>0.03183459843716613</v>
+        <v>0.03172127006595307</v>
       </c>
     </row>
     <row r="4">
